--- a/pacientes.xlsx
+++ b/pacientes.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6527" uniqueCount="1745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6574" uniqueCount="1769">
   <si>
     <t xml:space="preserve">REGISTRO MAESTRO DE PACIENTES – SISMO VENEZUELA 2026</t>
   </si>
@@ -5112,6 +5112,75 @@
     <t xml:space="preserve">BAZZAN YUSSEF</t>
   </si>
   <si>
+    <t xml:space="preserve">AARON VILLABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESAR CHERMETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATIALIO ROMERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATIAS JIMENEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALFREDO QUINTANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON MENDOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAXIMILIANO CHIRINOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASHLY CARREÑO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERECHO CARREÑO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISABELLA REBOREDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMA MALAVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMILY RAMOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YOISBELYS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YONIELBYS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDUANYELIS PEREZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">HOSPITAL DOMINGO LUCIANI</t>
   </si>
   <si>
@@ -5221,6 +5290,9 @@
   </si>
   <si>
     <t xml:space="preserve">18384289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AARON VILLALBA</t>
   </si>
   <si>
     <t xml:space="preserve">CRUZ ROJA</t>
@@ -5503,79 +5575,79 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5831,8 +5903,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H909"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H924"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -23840,6 +23912,212 @@
         <v>1118</v>
       </c>
       <c r="H909" s="15"/>
+    </row>
+    <row r="910" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A910" s="10" t="n">
+        <v>858</v>
+      </c>
+      <c r="B910" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C910" s="10" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D910" s="10" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="911" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A911" s="10" t="n">
+        <v>859</v>
+      </c>
+      <c r="B911" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C911" s="10" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D911" s="10" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A912" s="10" t="n">
+        <v>860</v>
+      </c>
+      <c r="B912" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C912" s="10" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D912" s="10" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="913" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A913" s="10" t="n">
+        <v>861</v>
+      </c>
+      <c r="B913" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C913" s="10" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D913" s="10" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="914" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A914" s="10" t="n">
+        <v>862</v>
+      </c>
+      <c r="B914" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C914" s="10" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D914" s="10"/>
+    </row>
+    <row r="915" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A915" s="10" t="n">
+        <v>863</v>
+      </c>
+      <c r="B915" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C915" s="10" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D915" s="10"/>
+    </row>
+    <row r="916" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A916" s="10" t="n">
+        <v>864</v>
+      </c>
+      <c r="B916" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C916" s="10" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D916" s="10" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="917" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A917" s="10" t="n">
+        <v>865</v>
+      </c>
+      <c r="B917" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C917" s="10" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D917" s="10" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="918" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A918" s="10" t="n">
+        <v>866</v>
+      </c>
+      <c r="B918" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C918" s="10" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D918" s="10" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="919" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A919" s="10" t="n">
+        <v>867</v>
+      </c>
+      <c r="B919" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C919" s="10" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D919" s="10" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="920" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A920" s="10" t="n">
+        <v>868</v>
+      </c>
+      <c r="B920" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C920" s="10" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D920" s="10" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="921" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A921" s="10" t="n">
+        <v>869</v>
+      </c>
+      <c r="B921" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C921" s="10" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D921" s="10" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="922" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A922" s="10" t="n">
+        <v>870</v>
+      </c>
+      <c r="B922" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C922" s="10" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D922" s="10" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="923" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A923" s="10" t="n">
+        <v>871</v>
+      </c>
+      <c r="B923" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C923" s="10" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D923" s="10" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="924" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A924" s="10" t="n">
+        <v>872</v>
+      </c>
+      <c r="B924" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C924" s="10" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D924" s="10" t="s">
+        <v>1712</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -23862,7 +24140,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G128"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -23875,7 +24153,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1737</v>
+        <v>1761</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -23898,10 +24176,10 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1738</v>
+        <v>1762</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1739</v>
+        <v>1763</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>9</v>
@@ -23919,7 +24197,7 @@
         <v>1117</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>1118</v>
@@ -23938,7 +24216,7 @@
         <v>1120</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>1118</v>
@@ -23959,7 +24237,7 @@
         <v>1122</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>1118</v>
@@ -23978,7 +24256,7 @@
         <v>1124</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>1118</v>
@@ -23997,7 +24275,7 @@
         <v>1126</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -24014,7 +24292,7 @@
         <v>1128</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>1118</v>
@@ -24035,7 +24313,7 @@
         <v>1130</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>1118</v>
@@ -24054,7 +24332,7 @@
         <v>1132</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>1118</v>
@@ -24073,7 +24351,7 @@
         <v>1134</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>1118</v>
@@ -24092,7 +24370,7 @@
         <v>1136</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>1118</v>
@@ -24111,7 +24389,7 @@
         <v>1138</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>1139</v>
@@ -24130,7 +24408,7 @@
         <v>1141</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>1741</v>
+        <v>1765</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>1118</v>
@@ -24149,7 +24427,7 @@
         <v>1143</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>1118</v>
@@ -24168,7 +24446,7 @@
         <v>1145</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>1741</v>
+        <v>1765</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>1118</v>
@@ -24187,7 +24465,7 @@
         <v>1147</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>1139</v>
@@ -24206,7 +24484,7 @@
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>1139</v>
@@ -24225,7 +24503,7 @@
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>1118</v>
@@ -24242,7 +24520,7 @@
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>1118</v>
@@ -24259,7 +24537,7 @@
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>1118</v>
@@ -24276,7 +24554,7 @@
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>1154</v>
@@ -24293,7 +24571,7 @@
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>1156</v>
@@ -24310,7 +24588,7 @@
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>1158</v>
@@ -24342,7 +24620,7 @@
         <v>1161</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>1139</v>
@@ -24361,7 +24639,7 @@
         <v>1163</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -24378,7 +24656,7 @@
         <v>1165</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -24395,7 +24673,7 @@
         <v>1167</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -24412,7 +24690,7 @@
         <v>1169</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>1741</v>
+        <v>1765</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -24427,7 +24705,7 @@
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -24442,7 +24720,7 @@
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
@@ -24459,7 +24737,7 @@
         <v>1173</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
@@ -24476,7 +24754,7 @@
         <v>1175</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>1176</v>
@@ -24495,7 +24773,7 @@
         <v>1178</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F35" s="15" t="s">
         <v>1118</v>
@@ -24514,7 +24792,7 @@
         <v>1180</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>1181</v>
@@ -24533,7 +24811,7 @@
         <v>1183</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>1181</v>
@@ -24552,7 +24830,7 @@
         <v>1185</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>1118</v>
@@ -24571,7 +24849,7 @@
         <v>1187</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>1118</v>
@@ -24590,7 +24868,7 @@
         <v>1189</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>1118</v>
@@ -24609,7 +24887,7 @@
         <v>1191</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F41" s="15" t="s">
         <v>1118</v>
@@ -24628,7 +24906,7 @@
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
       <c r="E42" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15" t="s">
@@ -24645,7 +24923,7 @@
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
       <c r="E43" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
@@ -24660,7 +24938,7 @@
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
       <c r="E44" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>1118</v>
@@ -24679,7 +24957,7 @@
         <v>1197</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>1198</v>
@@ -24698,7 +24976,7 @@
         <v>1200</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>1118</v>
@@ -24715,7 +24993,7 @@
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>1202</v>
@@ -24734,7 +25012,7 @@
         <v>1204</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>1118</v>
@@ -24751,7 +25029,7 @@
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>1206</v>
@@ -24770,7 +25048,7 @@
         <v>1208</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>1118</v>
@@ -24789,7 +25067,7 @@
         <v>1210</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>1741</v>
+        <v>1765</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>1118</v>
@@ -24808,7 +25086,7 @@
         <v>1212</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>1741</v>
+        <v>1765</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>1118</v>
@@ -24829,7 +25107,7 @@
         <v>1215</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>1741</v>
+        <v>1765</v>
       </c>
       <c r="F53" s="15" t="s">
         <v>1118</v>
@@ -24848,7 +25126,7 @@
         <v>1217</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>1218</v>
@@ -24865,7 +25143,7 @@
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
       <c r="E55" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="s">
@@ -24882,7 +25160,7 @@
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
       <c r="E56" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>1118</v>
@@ -24901,7 +25179,7 @@
         <v>1175</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>1740</v>
+        <v>1764</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>1221</v>
@@ -25913,7 +26191,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G153"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35"/>
@@ -25926,7 +26204,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>1742</v>
+        <v>1766</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -25949,10 +26227,10 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1739</v>
+        <v>1763</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1743</v>
+        <v>1767</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -29131,20 +29409,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1744</v>
+        <v>1768</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -29638,7 +29916,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G175"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -29650,7 +29928,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1693</v>
+        <v>1716</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -32415,7 +32693,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G133"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -32427,7 +32705,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1694</v>
+        <v>1717</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -33058,13 +33336,13 @@
         <v>187</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>1695</v>
+        <v>1718</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>1696</v>
+        <v>1719</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1697</v>
+        <v>1720</v>
       </c>
       <c r="G31" s="11"/>
     </row>
@@ -33601,7 +33879,7 @@
         <v>672</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>1698</v>
+        <v>1721</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>626</v>
@@ -33700,10 +33978,10 @@
       </c>
       <c r="D62" s="11"/>
       <c r="E62" s="11" t="s">
-        <v>1699</v>
+        <v>1722</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>1700</v>
+        <v>1723</v>
       </c>
       <c r="G62" s="11"/>
     </row>
@@ -33757,7 +34035,7 @@
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="11" t="s">
-        <v>1701</v>
+        <v>1724</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>1013</v>
@@ -33776,10 +34054,10 @@
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="11" t="s">
-        <v>1702</v>
+        <v>1725</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>1703</v>
+        <v>1726</v>
       </c>
       <c r="G66" s="11"/>
     </row>
@@ -33795,10 +34073,10 @@
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
-        <v>1704</v>
+        <v>1727</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>1705</v>
+        <v>1728</v>
       </c>
       <c r="G67" s="11"/>
     </row>
@@ -33814,10 +34092,10 @@
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>1706</v>
+        <v>1729</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>1707</v>
+        <v>1730</v>
       </c>
       <c r="G68" s="11"/>
     </row>
@@ -33833,10 +34111,10 @@
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
-        <v>1708</v>
+        <v>1731</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>1709</v>
+        <v>1732</v>
       </c>
       <c r="G69" s="11"/>
     </row>
@@ -33853,7 +34131,7 @@
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
       <c r="F70" s="11" t="s">
-        <v>1710</v>
+        <v>1733</v>
       </c>
       <c r="G70" s="11"/>
     </row>
@@ -33869,10 +34147,10 @@
       </c>
       <c r="D71" s="11"/>
       <c r="E71" s="11" t="s">
-        <v>1711</v>
+        <v>1734</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>1712</v>
+        <v>1735</v>
       </c>
       <c r="G71" s="11"/>
     </row>
@@ -33907,10 +34185,10 @@
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
-        <v>1713</v>
+        <v>1736</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>1714</v>
+        <v>1737</v>
       </c>
       <c r="G73" s="11"/>
     </row>
@@ -33926,7 +34204,7 @@
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
-        <v>1715</v>
+        <v>1738</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>806</v>
@@ -33945,7 +34223,7 @@
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
-        <v>1716</v>
+        <v>1739</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>63</v>
@@ -33964,7 +34242,7 @@
       </c>
       <c r="D76" s="11"/>
       <c r="E76" s="11" t="s">
-        <v>1717</v>
+        <v>1740</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>63</v>
@@ -34051,7 +34329,7 @@
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11" t="s">
-        <v>1718</v>
+        <v>1741</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>63</v>
@@ -35163,8 +35441,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G140"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -35176,7 +35454,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1719</v>
+        <v>1742</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -36332,7 +36610,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>1720</v>
+        <v>1743</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10" t="s">
@@ -36409,7 +36687,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>1721</v>
+        <v>1744</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10" t="s">
@@ -36801,7 +37079,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>1722</v>
+        <v>1745</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="10" t="s">
@@ -36831,7 +37109,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>1723</v>
+        <v>1746</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="10" t="s">
@@ -36981,7 +37259,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="10" t="s">
-        <v>1724</v>
+        <v>1747</v>
       </c>
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
@@ -37118,7 +37396,7 @@
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="10" t="s">
-        <v>1725</v>
+        <v>1748</v>
       </c>
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
@@ -37148,7 +37426,7 @@
       </c>
       <c r="C132" s="10"/>
       <c r="D132" s="10" t="s">
-        <v>1726</v>
+        <v>1749</v>
       </c>
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
@@ -37178,7 +37456,7 @@
       </c>
       <c r="C134" s="10"/>
       <c r="D134" s="10" t="s">
-        <v>1727</v>
+        <v>1750</v>
       </c>
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
@@ -37193,7 +37471,7 @@
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="10" t="s">
-        <v>1728</v>
+        <v>1751</v>
       </c>
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
@@ -37223,11 +37501,38 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="10" t="s">
-        <v>1729</v>
+        <v>1752</v>
       </c>
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
       <c r="G137" s="10"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -37249,7 +37554,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -37261,7 +37566,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1730</v>
+        <v>1754</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -37776,7 +38081,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -37788,7 +38093,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1731</v>
+        <v>1755</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -39263,7 +39568,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -39275,7 +39580,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1732</v>
+        <v>1756</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -39482,7 +39787,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -39494,7 +39799,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1733</v>
+        <v>1757</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -39862,7 +40167,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -39874,7 +40179,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1734</v>
+        <v>1758</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -39903,7 +40208,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>1735</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40139,7 +40444,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1736</v>
+        <v>1760</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>80</v>

--- a/pacientes.xlsx
+++ b/pacientes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="🔍 BUSCAR PACIENTES" sheetId="1" state="visible" r:id="rId3"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6574" uniqueCount="1769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6597" uniqueCount="1767">
   <si>
     <t xml:space="preserve">REGISTRO MAESTRO DE PACIENTES – SISMO VENEZUELA 2026</t>
   </si>
@@ -5287,12 +5287,6 @@
   </si>
   <si>
     <t xml:space="preserve">13717087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18384289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AARON VILLALBA</t>
   </si>
   <si>
     <t xml:space="preserve">CRUZ ROJA</t>
@@ -24153,7 +24147,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -24176,10 +24170,10 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>9</v>
@@ -24197,7 +24191,7 @@
         <v>1117</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>1118</v>
@@ -24216,7 +24210,7 @@
         <v>1120</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>1118</v>
@@ -24237,7 +24231,7 @@
         <v>1122</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>1118</v>
@@ -24256,7 +24250,7 @@
         <v>1124</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>1118</v>
@@ -24275,7 +24269,7 @@
         <v>1126</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -24292,7 +24286,7 @@
         <v>1128</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>1118</v>
@@ -24313,7 +24307,7 @@
         <v>1130</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>1118</v>
@@ -24332,7 +24326,7 @@
         <v>1132</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>1118</v>
@@ -24351,7 +24345,7 @@
         <v>1134</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>1118</v>
@@ -24370,7 +24364,7 @@
         <v>1136</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>1118</v>
@@ -24389,7 +24383,7 @@
         <v>1138</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>1139</v>
@@ -24408,7 +24402,7 @@
         <v>1141</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>1118</v>
@@ -24427,7 +24421,7 @@
         <v>1143</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>1118</v>
@@ -24446,7 +24440,7 @@
         <v>1145</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>1118</v>
@@ -24465,7 +24459,7 @@
         <v>1147</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>1139</v>
@@ -24484,7 +24478,7 @@
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>1139</v>
@@ -24503,7 +24497,7 @@
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>1118</v>
@@ -24520,7 +24514,7 @@
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>1118</v>
@@ -24537,7 +24531,7 @@
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>1118</v>
@@ -24554,7 +24548,7 @@
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>1154</v>
@@ -24571,7 +24565,7 @@
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>1156</v>
@@ -24588,7 +24582,7 @@
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>1158</v>
@@ -24620,7 +24614,7 @@
         <v>1161</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>1139</v>
@@ -24639,7 +24633,7 @@
         <v>1163</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -24656,7 +24650,7 @@
         <v>1165</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -24673,7 +24667,7 @@
         <v>1167</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -24690,7 +24684,7 @@
         <v>1169</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -24705,7 +24699,7 @@
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -24720,7 +24714,7 @@
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
@@ -24737,7 +24731,7 @@
         <v>1173</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
@@ -24754,7 +24748,7 @@
         <v>1175</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>1176</v>
@@ -24773,7 +24767,7 @@
         <v>1178</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F35" s="15" t="s">
         <v>1118</v>
@@ -24792,7 +24786,7 @@
         <v>1180</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>1181</v>
@@ -24811,7 +24805,7 @@
         <v>1183</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>1181</v>
@@ -24830,7 +24824,7 @@
         <v>1185</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>1118</v>
@@ -24849,7 +24843,7 @@
         <v>1187</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>1118</v>
@@ -24868,7 +24862,7 @@
         <v>1189</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>1118</v>
@@ -24887,7 +24881,7 @@
         <v>1191</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F41" s="15" t="s">
         <v>1118</v>
@@ -24906,7 +24900,7 @@
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
       <c r="E42" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15" t="s">
@@ -24923,7 +24917,7 @@
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
       <c r="E43" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
@@ -24938,7 +24932,7 @@
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
       <c r="E44" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>1118</v>
@@ -24957,7 +24951,7 @@
         <v>1197</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>1198</v>
@@ -24976,7 +24970,7 @@
         <v>1200</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>1118</v>
@@ -24993,7 +24987,7 @@
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>1202</v>
@@ -25012,7 +25006,7 @@
         <v>1204</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>1118</v>
@@ -25029,7 +25023,7 @@
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>1206</v>
@@ -25048,7 +25042,7 @@
         <v>1208</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>1118</v>
@@ -25067,7 +25061,7 @@
         <v>1210</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>1118</v>
@@ -25086,7 +25080,7 @@
         <v>1212</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>1118</v>
@@ -25107,7 +25101,7 @@
         <v>1215</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F53" s="15" t="s">
         <v>1118</v>
@@ -25126,7 +25120,7 @@
         <v>1217</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>1218</v>
@@ -25143,7 +25137,7 @@
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
       <c r="E55" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="s">
@@ -25160,7 +25154,7 @@
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
       <c r="E56" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>1118</v>
@@ -25179,7 +25173,7 @@
         <v>1175</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>1221</v>
@@ -26204,7 +26198,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -26227,10 +26221,10 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -29422,7 +29416,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -35441,7 +35435,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -37500,39 +37494,267 @@
         <v>522</v>
       </c>
       <c r="C137" s="10"/>
-      <c r="D137" s="10" t="s">
-        <v>1752</v>
-      </c>
+      <c r="D137" s="10"/>
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
       <c r="G137" s="10"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="10" t="n">
         <v>136</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C138" s="1" t="s">
+      <c r="B138" s="10" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C138" s="10" t="s">
         <v>1694</v>
       </c>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="10"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="10" t="n">
         <v>137</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="10" t="s">
         <v>1695</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="10" t="s">
         <v>1696</v>
       </c>
+      <c r="D139" s="10"/>
+      <c r="E139" s="10"/>
+      <c r="F139" s="10"/>
+      <c r="G139" s="10"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="10" t="n">
         <v>138</v>
       </c>
+      <c r="B140" s="10" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="F140" s="10"/>
+      <c r="G140" s="10"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D141" s="10"/>
+      <c r="E141" s="10"/>
+      <c r="F141" s="10"/>
+      <c r="G141" s="10"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C142" s="10"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
+      <c r="G142" s="10"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
+      <c r="G143" s="10"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10"/>
+      <c r="F144" s="10"/>
+      <c r="G144" s="10"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="10"/>
+      <c r="G145" s="10"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D146" s="10"/>
+      <c r="E146" s="10"/>
+      <c r="F146" s="10"/>
+      <c r="G146" s="10"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D147" s="10"/>
+      <c r="E147" s="10"/>
+      <c r="F147" s="10"/>
+      <c r="G147" s="10"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D148" s="10"/>
+      <c r="E148" s="10"/>
+      <c r="F148" s="10"/>
+      <c r="G148" s="10"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D149" s="10"/>
+      <c r="E149" s="10"/>
+      <c r="F149" s="10"/>
+      <c r="G149" s="10"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D150" s="10"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="10"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D151" s="10"/>
+      <c r="E151" s="10"/>
+      <c r="F151" s="10"/>
+      <c r="G151" s="10"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D152" s="10"/>
+      <c r="E152" s="10"/>
+      <c r="F152" s="10"/>
+      <c r="G152" s="10"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="10"/>
+      <c r="B153" s="10"/>
+      <c r="C153" s="10"/>
+      <c r="D153" s="10"/>
+      <c r="E153" s="10"/>
+      <c r="F153" s="10"/>
+      <c r="G153" s="10"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="10"/>
+      <c r="B154" s="10"/>
+      <c r="C154" s="10"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="10"/>
+      <c r="F154" s="10"/>
+      <c r="G154" s="10"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="10"/>
+      <c r="B155" s="10"/>
+      <c r="C155" s="10"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
+      <c r="C156" s="10"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="10"/>
+      <c r="F156" s="10"/>
+      <c r="G156" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -37566,7 +37788,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -38093,7 +38315,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -39580,7 +39802,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -39799,7 +40021,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -40179,7 +40401,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -40208,7 +40430,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40444,7 +40666,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>80</v>
